--- a/ExcelFiles/ModelBaseline5Sectorsand1Regions_replication.xlsx
+++ b/ExcelFiles/ModelBaseline5Sectorsand1Regions_replication.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\GitHub\DGE-METRIC\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nb\Documents\GitHub\DGE-METRIC-VietNam\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AA3219-8666-435E-A00B-0B436037EC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2580FC-0093-49DD-A484-AB9F70D11492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31632" yWindow="1488" windowWidth="28800" windowHeight="15216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Sheets</t>
   </si>
@@ -442,6 +442,9 @@
   </si>
   <si>
     <t>idx_PV_1_plan_inv</t>
+  </si>
+  <si>
+    <t>exo_lE_NOETS_Target_1_1</t>
   </si>
 </sst>
 </file>
@@ -915,12 +918,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DV27"/>
+  <dimension ref="A1:DW27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -934,40 +940,50 @@
     <col min="42" max="42" width="10" bestFit="1" customWidth="1"/>
     <col min="43" max="47" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="54" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="55" max="61" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="2.140625" bestFit="1" customWidth="1"/>
     <col min="62" max="63" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="65" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="2.140625" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="15" bestFit="1" customWidth="1"/>
-    <col min="69" max="73" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="74" max="78" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="79" max="83" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="12" bestFit="1" customWidth="1"/>
-    <col min="86" max="90" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="12" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="93" max="97" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="98" max="102" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="103" max="107" width="18" bestFit="1" customWidth="1"/>
-    <col min="108" max="112" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="115" max="116" width="14" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="121" max="122" width="12" bestFit="1" customWidth="1"/>
-    <col min="123" max="124" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="18" bestFit="1" customWidth="1"/>
+    <col min="69" max="79" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="81" max="84" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="86" max="88" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="90" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="95" max="97" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="100" max="102" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="18" bestFit="1" customWidth="1"/>
+    <col min="104" max="105" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="106" max="107" width="18" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="111" max="112" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="114" max="115" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="116" max="119" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="121" max="122" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="123" max="126" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="2.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1346,8 +1362,11 @@
       <c r="DV1" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="DW1" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="2" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -1726,8 +1745,11 @@
       <c r="DV2">
         <v>1</v>
       </c>
+      <c r="DW2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -2106,8 +2128,11 @@
       <c r="DV3">
         <v>2.4356709000552166</v>
       </c>
+      <c r="DW3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -2486,8 +2511,11 @@
       <c r="DV4">
         <v>3.9983434566537834</v>
       </c>
+      <c r="DW4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -2866,8 +2894,11 @@
       <c r="DV5">
         <v>10.22528989508559</v>
       </c>
+      <c r="DW5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -3246,8 +3277,11 @@
       <c r="DV6">
         <v>19.789618995030366</v>
       </c>
+      <c r="DW6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -3626,8 +3660,11 @@
       <c r="DV7">
         <v>7.7020430701269982</v>
       </c>
+      <c r="DW7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4006,8 +4043,11 @@
       <c r="DV8">
         <v>8.0665709552733258</v>
       </c>
+      <c r="DW8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4386,8 +4426,11 @@
       <c r="DV9">
         <v>8.4310988404196596</v>
       </c>
+      <c r="DW9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4766,8 +4809,11 @@
       <c r="DV10">
         <v>8.7956267255659792</v>
       </c>
+      <c r="DW10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -5146,8 +5192,11 @@
       <c r="DV11">
         <v>9.1601546107123166</v>
       </c>
+      <c r="DW11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -5526,8 +5575,11 @@
       <c r="DV12">
         <v>13.566206515737163</v>
       </c>
+      <c r="DW12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -5906,8 +5958,11 @@
       <c r="DV13">
         <v>14.334886802871347</v>
       </c>
+      <c r="DW13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -6286,8 +6341,11 @@
       <c r="DV14">
         <v>15.103567090005514</v>
       </c>
+      <c r="DW14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -6666,8 +6724,11 @@
       <c r="DV15">
         <v>15.872247377139708</v>
       </c>
+      <c r="DW15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -7046,8 +7107,11 @@
       <c r="DV16">
         <v>16.640927664273875</v>
       </c>
+      <c r="DW16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -7426,8 +7490,11 @@
       <c r="DV17">
         <v>18.240750966316952</v>
       </c>
+      <c r="DW17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -7806,8 +7873,11 @@
       <c r="DV18">
         <v>19.092545554942006</v>
       </c>
+      <c r="DW18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -8186,8 +8256,11 @@
       <c r="DV19">
         <v>19.944340143567079</v>
       </c>
+      <c r="DW19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -8566,8 +8639,11 @@
       <c r="DV20">
         <v>20.796134732192169</v>
       </c>
+      <c r="DW20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -8946,8 +9022,11 @@
       <c r="DV21">
         <v>21.647929320817223</v>
       </c>
+      <c r="DW21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -9326,8 +9405,11 @@
       <c r="DV22">
         <v>16.425731639977919</v>
       </c>
+      <c r="DW22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
@@ -9706,8 +9788,11 @@
       <c r="DV23">
         <v>16.670127001656532</v>
       </c>
+      <c r="DW23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
@@ -10086,8 +10171,11 @@
       <c r="DV24">
         <v>16.91452236333518</v>
       </c>
+      <c r="DW24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -10466,8 +10554,11 @@
       <c r="DV25">
         <v>17.158917725013811</v>
       </c>
+      <c r="DW25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
@@ -10781,7 +10872,7 @@
         <v>1</v>
       </c>
       <c r="DA26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB26">
         <v>0</v>
@@ -10846,8 +10937,11 @@
       <c r="DV26">
         <v>17.403313086692442</v>
       </c>
+      <c r="DW26">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:126" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:127" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
@@ -11225,6 +11319,9 @@
       </c>
       <c r="DV27">
         <v>15.203754831584764</v>
+      </c>
+      <c r="DW27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
